--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -479,16 +479,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317481</v>
+        <v>0.7593726906317482</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09836844935773284</v>
+        <v>0.0983684493577328</v>
       </c>
       <c r="D2" t="n">
-        <v>7.719677351730594</v>
+        <v>7.719677351730598</v>
       </c>
       <c r="E2" t="n">
-        <v>1.166245428296818e-14</v>
+        <v>1.166245428296781e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6461324144175187</v>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784786</v>
+        <v>0.5086498402784787</v>
       </c>
       <c r="C3" t="n">
         <v>0.2497200161268359</v>
@@ -519,7 +519,7 @@
         <v>0.04166201509511588</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06813509891921987</v>
+        <v>0.06813509891921965</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7853271920647402</v>
+        <v>0.78532719206474</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08298603259787436</v>
+        <v>0.08298603259787443</v>
       </c>
       <c r="D4" t="n">
-        <v>9.463365912071039</v>
+        <v>9.463365912071028</v>
       </c>
       <c r="E4" t="n">
-        <v>2.981867513211221e-21</v>
+        <v>2.981867513211542e-21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5665963324726649</v>
+        <v>0.5665963324726648</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384844</v>
+        <v>0.7448215921384848</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08844092520571627</v>
+        <v>0.08844092520571625</v>
       </c>
       <c r="D5" t="n">
-        <v>8.421684761958414</v>
+        <v>8.421684761958419</v>
       </c>
       <c r="E5" t="n">
-        <v>3.71108497441205e-17</v>
+        <v>3.711084974411862e-17</v>
       </c>
       <c r="F5" t="n">
         <v>0.5322519496799432</v>
@@ -601,7 +601,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5226161616438584</v>
+        <v>0.5226161616438579</v>
       </c>
       <c r="C2" t="n">
-        <v>8.586137185971867e-05</v>
+        <v>8.586137185971862e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.458742931602504</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04686770450590955</v>
+        <v>-0.04686770450590978</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7373004278414825</v>
+        <v>0.7373004278414815</v>
       </c>
       <c r="D3" t="n">
         <v>1.138253472208504</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3502322748046929</v>
+        <v>0.3502322748046926</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001386710077750266</v>
+        <v>0.001386710077750284</v>
       </c>
       <c r="D4" t="n">
         <v>2.517208064570842</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009252282929502659</v>
+        <v>-0.009252282929502639</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6548326921534757</v>
+        <v>0.6548326921534766</v>
       </c>
     </row>
     <row r="7">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9751202219394084</v>
+        <v>0.9751202219394079</v>
       </c>
     </row>
   </sheetData>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317481</v>
+        <v>0.7593726906317482</v>
       </c>
       <c r="C2" t="n">
-        <v>1.166245428296818e-14</v>
+        <v>1.166245428296781e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6461324144175187</v>
@@ -817,10 +817,10 @@
         <v>0.1178420405386001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1233470982376356</v>
+        <v>0.1233470982376352</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01611484024392051</v>
+        <v>0.01611484024392029</v>
       </c>
     </row>
     <row r="3">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784786</v>
+        <v>0.5086498402784787</v>
       </c>
       <c r="C3" t="n">
         <v>0.04166201509511588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06813509891921987</v>
+        <v>0.06813509891921965</v>
       </c>
       <c r="E3" t="n">
         <v>0.360980915943826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06654004160048281</v>
+        <v>0.0665400416004828</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03531899880137612</v>
+        <v>0.03531899880137623</v>
       </c>
     </row>
     <row r="4">
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7853271920647402</v>
+        <v>0.78532719206474</v>
       </c>
       <c r="C4" t="n">
-        <v>2.981867513211221e-21</v>
+        <v>2.981867513211542e-21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5665963324726649</v>
+        <v>0.5665963324726648</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07271647745080445</v>
+        <v>0.07271647745080442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4807484340336482</v>
+        <v>0.4807484340336489</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005035285214519902</v>
+        <v>0.00503528521451968</v>
       </c>
     </row>
     <row r="5">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384844</v>
+        <v>0.7448215921384848</v>
       </c>
       <c r="C5" t="n">
-        <v>3.71108497441205e-17</v>
+        <v>3.711084974411862e-17</v>
       </c>
       <c r="D5" t="n">
         <v>0.5322519496799432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06931932641661417</v>
+        <v>0.06931932641661419</v>
       </c>
       <c r="F5" t="n">
-        <v>0.51179177307778</v>
+        <v>0.5117917730777795</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004762160497665646</v>
+        <v>0.004762160497665757</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1736,7 @@
         <v>-6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2969076407959028</v>
+        <v>0.2969076407959024</v>
       </c>
     </row>
     <row r="3">
@@ -1744,7 +1744,7 @@
         <v>-5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3559256866438186</v>
+        <v>0.3559256866438181</v>
       </c>
     </row>
     <row r="4">
@@ -1752,7 +1752,7 @@
         <v>-4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.547926958622759</v>
+        <v>0.5479269586227599</v>
       </c>
     </row>
     <row r="5">
@@ -1760,7 +1760,7 @@
         <v>-3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1661982052222604</v>
+        <v>0.1661982052222608</v>
       </c>
     </row>
     <row r="6">
@@ -1776,7 +1776,7 @@
         <v>-1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5492825049004876</v>
+        <v>0.5492825049004871</v>
       </c>
     </row>
     <row r="8">
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3134115401229955</v>
+        <v>0.3134115401229951</v>
       </c>
     </row>
     <row r="9">
@@ -1792,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5619617865109332</v>
+        <v>0.5619617865109323</v>
       </c>
     </row>
     <row r="10">
@@ -1808,7 +1808,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.229897865760409</v>
+        <v>0.2298978657604095</v>
       </c>
     </row>
     <row r="12">
@@ -1816,7 +1816,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4053716036899732</v>
+        <v>0.4053716036899744</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1824,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3069967728675166</v>
+        <v>0.3069967728675165</v>
       </c>
     </row>
     <row r="14">
@@ -1832,7 +1832,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1431162796593948</v>
+        <v>0.1431162796593947</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -479,16 +479,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317482</v>
+        <v>0.7593726906317481</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0983684493577328</v>
+        <v>0.09836844935773284</v>
       </c>
       <c r="D2" t="n">
-        <v>7.719677351730598</v>
+        <v>7.719677351730594</v>
       </c>
       <c r="E2" t="n">
-        <v>1.166245428296781e-14</v>
+        <v>1.166245428296818e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6461324144175187</v>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784787</v>
+        <v>0.5086498402784786</v>
       </c>
       <c r="C3" t="n">
         <v>0.2497200161268359</v>
@@ -519,7 +519,7 @@
         <v>0.04166201509511588</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06813509891921965</v>
+        <v>0.06813509891921987</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.78532719206474</v>
+        <v>0.7853271920647402</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08298603259787443</v>
+        <v>0.08298603259787436</v>
       </c>
       <c r="D4" t="n">
-        <v>9.463365912071028</v>
+        <v>9.463365912071039</v>
       </c>
       <c r="E4" t="n">
-        <v>2.981867513211542e-21</v>
+        <v>2.981867513211221e-21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5665963324726648</v>
+        <v>0.5665963324726649</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384848</v>
+        <v>0.7448215921384844</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08844092520571625</v>
+        <v>0.08844092520571627</v>
       </c>
       <c r="D5" t="n">
-        <v>8.421684761958419</v>
+        <v>8.421684761958414</v>
       </c>
       <c r="E5" t="n">
-        <v>3.711084974411862e-17</v>
+        <v>3.71108497441205e-17</v>
       </c>
       <c r="F5" t="n">
         <v>0.5322519496799432</v>
@@ -601,7 +601,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5226161616438579</v>
+        <v>0.5226161616438584</v>
       </c>
       <c r="C2" t="n">
-        <v>8.586137185971862e-05</v>
+        <v>8.586137185971867e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.458742931602504</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04686770450590978</v>
+        <v>-0.04686770450590955</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7373004278414815</v>
+        <v>0.7373004278414825</v>
       </c>
       <c r="D3" t="n">
         <v>1.138253472208504</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3502322748046926</v>
+        <v>0.3502322748046929</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001386710077750284</v>
+        <v>0.001386710077750266</v>
       </c>
       <c r="D4" t="n">
         <v>2.517208064570842</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009252282929502639</v>
+        <v>-0.009252282929502659</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6548326921534766</v>
+        <v>0.6548326921534757</v>
       </c>
     </row>
     <row r="7">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9751202219394079</v>
+        <v>0.9751202219394084</v>
       </c>
     </row>
   </sheetData>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317482</v>
+        <v>0.7593726906317481</v>
       </c>
       <c r="C2" t="n">
-        <v>1.166245428296781e-14</v>
+        <v>1.166245428296818e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6461324144175187</v>
@@ -817,10 +817,10 @@
         <v>0.1178420405386001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1233470982376352</v>
+        <v>0.1233470982376356</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01611484024392029</v>
+        <v>0.01611484024392051</v>
       </c>
     </row>
     <row r="3">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784787</v>
+        <v>0.5086498402784786</v>
       </c>
       <c r="C3" t="n">
         <v>0.04166201509511588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06813509891921965</v>
+        <v>0.06813509891921987</v>
       </c>
       <c r="E3" t="n">
         <v>0.360980915943826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0665400416004828</v>
+        <v>0.06654004160048281</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03531899880137623</v>
+        <v>0.03531899880137612</v>
       </c>
     </row>
     <row r="4">
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.78532719206474</v>
+        <v>0.7853271920647402</v>
       </c>
       <c r="C4" t="n">
-        <v>2.981867513211542e-21</v>
+        <v>2.981867513211221e-21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5665963324726648</v>
+        <v>0.5665963324726649</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07271647745080442</v>
+        <v>0.07271647745080445</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4807484340336489</v>
+        <v>0.4807484340336482</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00503528521451968</v>
+        <v>0.005035285214519902</v>
       </c>
     </row>
     <row r="5">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384848</v>
+        <v>0.7448215921384844</v>
       </c>
       <c r="C5" t="n">
-        <v>3.711084974411862e-17</v>
+        <v>3.71108497441205e-17</v>
       </c>
       <c r="D5" t="n">
         <v>0.5322519496799432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06931932641661419</v>
+        <v>0.06931932641661417</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5117917730777795</v>
+        <v>0.51179177307778</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004762160497665757</v>
+        <v>0.004762160497665646</v>
       </c>
     </row>
   </sheetData>
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1699,6 +1699,19 @@
       </c>
       <c r="C60" t="n">
         <v>1.75</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1749,7 @@
         <v>-6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2969076407959024</v>
+        <v>0.2976511656361512</v>
       </c>
     </row>
     <row r="3">
@@ -1744,7 +1757,7 @@
         <v>-5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3559256866438181</v>
+        <v>0.3566248739311924</v>
       </c>
     </row>
     <row r="4">
@@ -1752,7 +1765,7 @@
         <v>-4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5479269586227599</v>
+        <v>0.5483961684511519</v>
       </c>
     </row>
     <row r="5">
@@ -1760,7 +1773,7 @@
         <v>-3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1661982052222608</v>
+        <v>0.167040601292703</v>
       </c>
     </row>
     <row r="6">
@@ -1768,7 +1781,7 @@
         <v>-2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5488476899617384</v>
+        <v>0.5492825049004877</v>
       </c>
     </row>
     <row r="7">
@@ -1776,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5492825049004871</v>
+        <v>0.5312969601400095</v>
       </c>
     </row>
     <row r="8">
@@ -1784,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3134115401229951</v>
+        <v>0.3011178656411544</v>
       </c>
     </row>
     <row r="9">
@@ -1792,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5619617865109323</v>
+        <v>0.544813323722413</v>
       </c>
     </row>
     <row r="10">
@@ -1800,7 +1813,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4852131751835659</v>
+        <v>0.4684837072372273</v>
       </c>
     </row>
     <row r="11">
@@ -1808,7 +1821,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2298978657604095</v>
+        <v>0.2183543475022114</v>
       </c>
     </row>
     <row r="12">
@@ -1816,7 +1829,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4053716036899744</v>
+        <v>0.3891470171057804</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1837,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3069967728675165</v>
+        <v>0.2928575123673366</v>
       </c>
     </row>
     <row r="14">
@@ -1832,7 +1845,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1431162796593947</v>
+        <v>0.1324934874139426</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="단순회귀(시장금리)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="다중회귀(시장금리)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="동월vs1개월선행" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="정책금리 스프레드" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="교차상관(한국-미국)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단순회귀(시장금리)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다중회귀(시장금리)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="동월vs1개월선행" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정책금리 스프레드" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="교차상관(한국-미국)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -479,16 +479,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317481</v>
+        <v>0.7593726906317482</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09836844935773284</v>
+        <v>0.0983684493577328</v>
       </c>
       <c r="D2" t="n">
-        <v>7.719677351730594</v>
+        <v>7.719677351730598</v>
       </c>
       <c r="E2" t="n">
-        <v>1.166245428296818e-14</v>
+        <v>1.166245428296781e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6461324144175187</v>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784786</v>
+        <v>0.5086498402784787</v>
       </c>
       <c r="C3" t="n">
         <v>0.2497200161268359</v>
@@ -519,7 +519,7 @@
         <v>0.04166201509511588</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06813509891921987</v>
+        <v>0.06813509891921965</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7853271920647402</v>
+        <v>0.78532719206474</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08298603259787436</v>
+        <v>0.08298603259787443</v>
       </c>
       <c r="D4" t="n">
-        <v>9.463365912071039</v>
+        <v>9.463365912071028</v>
       </c>
       <c r="E4" t="n">
-        <v>2.981867513211221e-21</v>
+        <v>2.981867513211542e-21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5665963324726649</v>
+        <v>0.5665963324726648</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384844</v>
+        <v>0.7448215921384848</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08844092520571627</v>
+        <v>0.08844092520571625</v>
       </c>
       <c r="D5" t="n">
-        <v>8.421684761958414</v>
+        <v>8.421684761958419</v>
       </c>
       <c r="E5" t="n">
-        <v>3.71108497441205e-17</v>
+        <v>3.711084974411862e-17</v>
       </c>
       <c r="F5" t="n">
         <v>0.5322519496799432</v>
@@ -601,7 +601,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5226161616438584</v>
+        <v>0.5226161616438579</v>
       </c>
       <c r="C2" t="n">
-        <v>8.586137185971867e-05</v>
+        <v>8.586137185971862e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.458742931602504</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04686770450590955</v>
+        <v>-0.04686770450590978</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7373004278414825</v>
+        <v>0.7373004278414815</v>
       </c>
       <c r="D3" t="n">
         <v>1.138253472208504</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3502322748046929</v>
+        <v>0.3502322748046926</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001386710077750266</v>
+        <v>0.001386710077750284</v>
       </c>
       <c r="D4" t="n">
         <v>2.517208064570842</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009252282929502659</v>
+        <v>-0.009252282929502639</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6548326921534757</v>
+        <v>0.6548326921534766</v>
       </c>
     </row>
     <row r="7">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9751202219394084</v>
+        <v>0.9751202219394079</v>
       </c>
     </row>
   </sheetData>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317481</v>
+        <v>0.7593726906317482</v>
       </c>
       <c r="C2" t="n">
-        <v>1.166245428296818e-14</v>
+        <v>1.166245428296781e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6461324144175187</v>
@@ -817,10 +817,10 @@
         <v>0.1178420405386001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1233470982376356</v>
+        <v>0.1233470982376352</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01611484024392051</v>
+        <v>0.01611484024392029</v>
       </c>
     </row>
     <row r="3">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784786</v>
+        <v>0.5086498402784787</v>
       </c>
       <c r="C3" t="n">
         <v>0.04166201509511588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06813509891921987</v>
+        <v>0.06813509891921965</v>
       </c>
       <c r="E3" t="n">
         <v>0.360980915943826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06654004160048281</v>
+        <v>0.0665400416004828</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03531899880137612</v>
+        <v>0.03531899880137623</v>
       </c>
     </row>
     <row r="4">
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7853271920647402</v>
+        <v>0.78532719206474</v>
       </c>
       <c r="C4" t="n">
-        <v>2.981867513211221e-21</v>
+        <v>2.981867513211542e-21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5665963324726649</v>
+        <v>0.5665963324726648</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07271647745080445</v>
+        <v>0.07271647745080442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4807484340336482</v>
+        <v>0.4807484340336489</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005035285214519902</v>
+        <v>0.00503528521451968</v>
       </c>
     </row>
     <row r="5">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384844</v>
+        <v>0.7448215921384848</v>
       </c>
       <c r="C5" t="n">
-        <v>3.71108497441205e-17</v>
+        <v>3.711084974411862e-17</v>
       </c>
       <c r="D5" t="n">
         <v>0.5322519496799432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06931932641661417</v>
+        <v>0.06931932641661419</v>
       </c>
       <c r="F5" t="n">
-        <v>0.51179177307778</v>
+        <v>0.5117917730777795</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004762160497665646</v>
+        <v>0.004762160497665757</v>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +1749,7 @@
         <v>-6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2976511656361512</v>
+        <v>0.2976511656361516</v>
       </c>
     </row>
     <row r="3">
@@ -1757,7 +1757,7 @@
         <v>-5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3566248739311924</v>
+        <v>0.3566248739311929</v>
       </c>
     </row>
     <row r="4">
@@ -1765,7 +1765,7 @@
         <v>-4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5483961684511519</v>
+        <v>0.5483961684511525</v>
       </c>
     </row>
     <row r="5">
@@ -1781,7 +1781,7 @@
         <v>-2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5492825049004877</v>
+        <v>0.5492825049004871</v>
       </c>
     </row>
     <row r="7">
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5312969601400095</v>
+        <v>0.5312969601400083</v>
       </c>
     </row>
     <row r="8">
@@ -1805,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.544813323722413</v>
+        <v>0.5448133237224131</v>
       </c>
     </row>
     <row r="10">
@@ -1813,7 +1813,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4684837072372273</v>
+        <v>0.4684837072372267</v>
       </c>
     </row>
     <row r="11">
@@ -1821,7 +1821,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2183543475022114</v>
+        <v>0.2183543475022113</v>
       </c>
     </row>
     <row r="12">
@@ -1829,7 +1829,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3891470171057804</v>
+        <v>0.3891470171057813</v>
       </c>
     </row>
     <row r="13">
@@ -1837,7 +1837,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2928575123673366</v>
+        <v>0.2928575123673372</v>
       </c>
     </row>
     <row r="14">
@@ -1845,7 +1845,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1324934874139426</v>
+        <v>0.1324934874139425</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -479,16 +479,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317482</v>
+        <v>0.7593726906317481</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0983684493577328</v>
+        <v>0.09836844935773284</v>
       </c>
       <c r="D2" t="n">
-        <v>7.719677351730598</v>
+        <v>7.719677351730594</v>
       </c>
       <c r="E2" t="n">
-        <v>1.166245428296781e-14</v>
+        <v>1.166245428296818e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6461324144175187</v>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784787</v>
+        <v>0.5086498402784786</v>
       </c>
       <c r="C3" t="n">
         <v>0.2497200161268359</v>
@@ -519,7 +519,7 @@
         <v>0.04166201509511588</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06813509891921965</v>
+        <v>0.06813509891921987</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.78532719206474</v>
+        <v>0.7853271920647402</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08298603259787443</v>
+        <v>0.08298603259787436</v>
       </c>
       <c r="D4" t="n">
-        <v>9.463365912071028</v>
+        <v>9.463365912071039</v>
       </c>
       <c r="E4" t="n">
-        <v>2.981867513211542e-21</v>
+        <v>2.981867513211221e-21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5665963324726648</v>
+        <v>0.5665963324726649</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384848</v>
+        <v>0.7448215921384844</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08844092520571625</v>
+        <v>0.08844092520571627</v>
       </c>
       <c r="D5" t="n">
-        <v>8.421684761958419</v>
+        <v>8.421684761958414</v>
       </c>
       <c r="E5" t="n">
-        <v>3.711084974411862e-17</v>
+        <v>3.71108497441205e-17</v>
       </c>
       <c r="F5" t="n">
         <v>0.5322519496799432</v>
@@ -601,7 +601,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5226161616438579</v>
+        <v>0.5226161616438584</v>
       </c>
       <c r="C2" t="n">
-        <v>8.586137185971862e-05</v>
+        <v>8.586137185971867e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.458742931602504</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04686770450590978</v>
+        <v>-0.04686770450590955</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7373004278414815</v>
+        <v>0.7373004278414825</v>
       </c>
       <c r="D3" t="n">
         <v>1.138253472208504</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3502322748046926</v>
+        <v>0.3502322748046929</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001386710077750284</v>
+        <v>0.001386710077750266</v>
       </c>
       <c r="D4" t="n">
         <v>2.517208064570842</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009252282929502639</v>
+        <v>-0.009252282929502659</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6548326921534766</v>
+        <v>0.6548326921534757</v>
       </c>
     </row>
     <row r="7">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9751202219394079</v>
+        <v>0.9751202219394084</v>
       </c>
     </row>
   </sheetData>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317482</v>
+        <v>0.7593726906317481</v>
       </c>
       <c r="C2" t="n">
-        <v>1.166245428296781e-14</v>
+        <v>1.166245428296818e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6461324144175187</v>
@@ -817,10 +817,10 @@
         <v>0.1178420405386001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1233470982376352</v>
+        <v>0.1233470982376356</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01611484024392029</v>
+        <v>0.01611484024392051</v>
       </c>
     </row>
     <row r="3">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784787</v>
+        <v>0.5086498402784786</v>
       </c>
       <c r="C3" t="n">
         <v>0.04166201509511588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06813509891921965</v>
+        <v>0.06813509891921987</v>
       </c>
       <c r="E3" t="n">
         <v>0.360980915943826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0665400416004828</v>
+        <v>0.06654004160048281</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03531899880137623</v>
+        <v>0.03531899880137612</v>
       </c>
     </row>
     <row r="4">
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.78532719206474</v>
+        <v>0.7853271920647402</v>
       </c>
       <c r="C4" t="n">
-        <v>2.981867513211542e-21</v>
+        <v>2.981867513211221e-21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5665963324726648</v>
+        <v>0.5665963324726649</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07271647745080442</v>
+        <v>0.07271647745080445</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4807484340336489</v>
+        <v>0.4807484340336482</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00503528521451968</v>
+        <v>0.005035285214519902</v>
       </c>
     </row>
     <row r="5">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384848</v>
+        <v>0.7448215921384844</v>
       </c>
       <c r="C5" t="n">
-        <v>3.711084974411862e-17</v>
+        <v>3.71108497441205e-17</v>
       </c>
       <c r="D5" t="n">
         <v>0.5322519496799432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06931932641661419</v>
+        <v>0.06931932641661417</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5117917730777795</v>
+        <v>0.51179177307778</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004762160497665757</v>
+        <v>0.004762160497665646</v>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +1749,7 @@
         <v>-6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2976511656361516</v>
+        <v>0.2976511656361512</v>
       </c>
     </row>
     <row r="3">
@@ -1757,7 +1757,7 @@
         <v>-5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3566248739311929</v>
+        <v>0.3566248739311924</v>
       </c>
     </row>
     <row r="4">
@@ -1765,7 +1765,7 @@
         <v>-4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5483961684511525</v>
+        <v>0.5483961684511519</v>
       </c>
     </row>
     <row r="5">
@@ -1781,7 +1781,7 @@
         <v>-2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5492825049004871</v>
+        <v>0.5492825049004877</v>
       </c>
     </row>
     <row r="7">
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5312969601400083</v>
+        <v>0.5312969601400095</v>
       </c>
     </row>
     <row r="8">
@@ -1805,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5448133237224131</v>
+        <v>0.544813323722413</v>
       </c>
     </row>
     <row r="10">
@@ -1813,7 +1813,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4684837072372267</v>
+        <v>0.4684837072372273</v>
       </c>
     </row>
     <row r="11">
@@ -1821,7 +1821,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2183543475022113</v>
+        <v>0.2183543475022114</v>
       </c>
     </row>
     <row r="12">
@@ -1829,7 +1829,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3891470171057813</v>
+        <v>0.3891470171057804</v>
       </c>
     </row>
     <row r="13">
@@ -1837,7 +1837,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2928575123673372</v>
+        <v>0.2928575123673366</v>
       </c>
     </row>
     <row r="14">
@@ -1845,7 +1845,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1324934874139425</v>
+        <v>0.1324934874139426</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -491,7 +491,7 @@
         <v>1.166245428296781e-14</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6461324144175187</v>
+        <v>0.6461324144175186</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -516,7 +516,7 @@
         <v>2.036880535920393</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04166201509511588</v>
+        <v>0.04166201509511585</v>
       </c>
       <c r="F3" t="n">
         <v>0.06813509891921965</v>
@@ -601,7 +601,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -636,7 +636,7 @@
         <v>0.5226161616438579</v>
       </c>
       <c r="C2" t="n">
-        <v>8.586137185971862e-05</v>
+        <v>8.586137185972025e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.458742931602504</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04686770450590978</v>
+        <v>-0.04686770450590967</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7373004278414815</v>
+        <v>0.7373004278414821</v>
       </c>
       <c r="D3" t="n">
         <v>1.138253472208504</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3502322748046926</v>
+        <v>0.3502322748046927</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001386710077750284</v>
+        <v>0.001386710077750293</v>
       </c>
       <c r="D4" t="n">
         <v>2.517208064570842</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009252282929502639</v>
+        <v>-0.009252282929502687</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6548326921534766</v>
+        <v>0.6548326921534746</v>
       </c>
     </row>
     <row r="7">
@@ -811,7 +811,7 @@
         <v>1.166245428296781e-14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6461324144175187</v>
+        <v>0.6461324144175186</v>
       </c>
       <c r="E2" t="n">
         <v>0.1178420405386001</v>
@@ -833,7 +833,7 @@
         <v>0.5086498402784787</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04166201509511588</v>
+        <v>0.04166201509511585</v>
       </c>
       <c r="D3" t="n">
         <v>0.06813509891921965</v>
@@ -845,7 +845,7 @@
         <v>0.0665400416004828</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03531899880137623</v>
+        <v>0.03531899880137612</v>
       </c>
     </row>
     <row r="4">
@@ -867,7 +867,7 @@
         <v>0.07271647745080442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4807484340336489</v>
+        <v>0.480748434033649</v>
       </c>
       <c r="G4" t="n">
         <v>0.00503528521451968</v>
@@ -889,10 +889,10 @@
         <v>0.5322519496799432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06931932641661419</v>
+        <v>0.06931932641661423</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5117917730777795</v>
+        <v>0.5117917730777792</v>
       </c>
       <c r="G5" t="n">
         <v>0.004762160497665757</v>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -491,7 +491,7 @@
         <v>1.166245428296781e-14</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6461324144175186</v>
+        <v>0.6461324144175187</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -516,7 +516,7 @@
         <v>2.036880535920393</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04166201509511585</v>
+        <v>0.04166201509511588</v>
       </c>
       <c r="F3" t="n">
         <v>0.06813509891921965</v>
@@ -601,7 +601,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -636,7 +636,7 @@
         <v>0.5226161616438579</v>
       </c>
       <c r="C2" t="n">
-        <v>8.586137185972025e-05</v>
+        <v>8.586137185971862e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.458742931602504</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04686770450590967</v>
+        <v>-0.04686770450590978</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7373004278414821</v>
+        <v>0.7373004278414815</v>
       </c>
       <c r="D3" t="n">
         <v>1.138253472208504</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3502322748046927</v>
+        <v>0.3502322748046926</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001386710077750293</v>
+        <v>0.001386710077750284</v>
       </c>
       <c r="D4" t="n">
         <v>2.517208064570842</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009252282929502687</v>
+        <v>-0.009252282929502639</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6548326921534746</v>
+        <v>0.6548326921534766</v>
       </c>
     </row>
     <row r="7">
@@ -811,7 +811,7 @@
         <v>1.166245428296781e-14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6461324144175186</v>
+        <v>0.6461324144175187</v>
       </c>
       <c r="E2" t="n">
         <v>0.1178420405386001</v>
@@ -833,7 +833,7 @@
         <v>0.5086498402784787</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04166201509511585</v>
+        <v>0.04166201509511588</v>
       </c>
       <c r="D3" t="n">
         <v>0.06813509891921965</v>
@@ -845,7 +845,7 @@
         <v>0.0665400416004828</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03531899880137612</v>
+        <v>0.03531899880137623</v>
       </c>
     </row>
     <row r="4">
@@ -867,7 +867,7 @@
         <v>0.07271647745080442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.480748434033649</v>
+        <v>0.4807484340336489</v>
       </c>
       <c r="G4" t="n">
         <v>0.00503528521451968</v>
@@ -889,10 +889,10 @@
         <v>0.5322519496799432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06931932641661423</v>
+        <v>0.06931932641661419</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5117917730777792</v>
+        <v>0.5117917730777795</v>
       </c>
       <c r="G5" t="n">
         <v>0.004762160497665757</v>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -479,19 +479,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317481</v>
+        <v>0.7593726906317482</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09836844935773284</v>
+        <v>0.0983684493577328</v>
       </c>
       <c r="D2" t="n">
-        <v>7.719677351730594</v>
+        <v>7.719677351730598</v>
       </c>
       <c r="E2" t="n">
-        <v>1.166245428296818e-14</v>
+        <v>1.166245428296781e-14</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6461324144175187</v>
+        <v>0.6461324144175186</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784786</v>
+        <v>0.5086498402784787</v>
       </c>
       <c r="C3" t="n">
         <v>0.2497200161268359</v>
@@ -516,10 +516,10 @@
         <v>2.036880535920393</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04166201509511588</v>
+        <v>0.04166201509511585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06813509891921987</v>
+        <v>0.06813509891921965</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7853271920647402</v>
+        <v>0.78532719206474</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08298603259787436</v>
+        <v>0.08298603259787443</v>
       </c>
       <c r="D4" t="n">
-        <v>9.463365912071039</v>
+        <v>9.463365912071028</v>
       </c>
       <c r="E4" t="n">
-        <v>2.981867513211221e-21</v>
+        <v>2.981867513211542e-21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5665963324726649</v>
+        <v>0.5665963324726648</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384844</v>
+        <v>0.7448215921384848</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08844092520571627</v>
+        <v>0.08844092520571625</v>
       </c>
       <c r="D5" t="n">
-        <v>8.421684761958414</v>
+        <v>8.421684761958419</v>
       </c>
       <c r="E5" t="n">
-        <v>3.71108497441205e-17</v>
+        <v>3.711084974411862e-17</v>
       </c>
       <c r="F5" t="n">
         <v>0.5322519496799432</v>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5226161616438584</v>
+        <v>0.5226161616438579</v>
       </c>
       <c r="C2" t="n">
-        <v>8.586137185971867e-05</v>
+        <v>8.586137185972025e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.458742931602504</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04686770450590955</v>
+        <v>-0.04686770450590967</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7373004278414825</v>
+        <v>0.7373004278414821</v>
       </c>
       <c r="D3" t="n">
         <v>1.138253472208504</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3502322748046929</v>
+        <v>0.3502322748046927</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001386710077750266</v>
+        <v>0.001386710077750293</v>
       </c>
       <c r="D4" t="n">
         <v>2.517208064570842</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009252282929502659</v>
+        <v>-0.009252282929502687</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6548326921534757</v>
+        <v>0.6548326921534746</v>
       </c>
     </row>
     <row r="7">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9751202219394084</v>
+        <v>0.9751202219394079</v>
       </c>
     </row>
   </sheetData>
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317481</v>
+        <v>0.7593726906317482</v>
       </c>
       <c r="C2" t="n">
-        <v>1.166245428296818e-14</v>
+        <v>1.166245428296781e-14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6461324144175187</v>
+        <v>0.6461324144175186</v>
       </c>
       <c r="E2" t="n">
         <v>0.1178420405386001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1233470982376356</v>
+        <v>0.1233470982376352</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01611484024392051</v>
+        <v>0.01611484024392029</v>
       </c>
     </row>
     <row r="3">
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784786</v>
+        <v>0.5086498402784787</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04166201509511588</v>
+        <v>0.04166201509511585</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06813509891921987</v>
+        <v>0.06813509891921965</v>
       </c>
       <c r="E3" t="n">
         <v>0.360980915943826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06654004160048281</v>
+        <v>0.0665400416004828</v>
       </c>
       <c r="G3" t="n">
         <v>0.03531899880137612</v>
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7853271920647402</v>
+        <v>0.78532719206474</v>
       </c>
       <c r="C4" t="n">
-        <v>2.981867513211221e-21</v>
+        <v>2.981867513211542e-21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5665963324726649</v>
+        <v>0.5665963324726648</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07271647745080445</v>
+        <v>0.07271647745080442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4807484340336482</v>
+        <v>0.480748434033649</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005035285214519902</v>
+        <v>0.00503528521451968</v>
       </c>
     </row>
     <row r="5">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384844</v>
+        <v>0.7448215921384848</v>
       </c>
       <c r="C5" t="n">
-        <v>3.71108497441205e-17</v>
+        <v>3.711084974411862e-17</v>
       </c>
       <c r="D5" t="n">
         <v>0.5322519496799432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06931932641661417</v>
+        <v>0.06931932641661423</v>
       </c>
       <c r="F5" t="n">
-        <v>0.51179177307778</v>
+        <v>0.5117917730777792</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004762160497665646</v>
+        <v>0.004762160497665757</v>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +1749,7 @@
         <v>-6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2976511656361512</v>
+        <v>0.2976511656361516</v>
       </c>
     </row>
     <row r="3">
@@ -1757,7 +1757,7 @@
         <v>-5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3566248739311924</v>
+        <v>0.3566248739311929</v>
       </c>
     </row>
     <row r="4">
@@ -1765,7 +1765,7 @@
         <v>-4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5483961684511519</v>
+        <v>0.5483961684511525</v>
       </c>
     </row>
     <row r="5">
@@ -1781,7 +1781,7 @@
         <v>-2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5492825049004877</v>
+        <v>0.5492825049004871</v>
       </c>
     </row>
     <row r="7">
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5312969601400095</v>
+        <v>0.5312969601400083</v>
       </c>
     </row>
     <row r="8">
@@ -1805,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.544813323722413</v>
+        <v>0.5448133237224131</v>
       </c>
     </row>
     <row r="10">
@@ -1813,7 +1813,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4684837072372273</v>
+        <v>0.4684837072372267</v>
       </c>
     </row>
     <row r="11">
@@ -1821,7 +1821,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2183543475022114</v>
+        <v>0.2183543475022113</v>
       </c>
     </row>
     <row r="12">
@@ -1829,7 +1829,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3891470171057804</v>
+        <v>0.3891470171057813</v>
       </c>
     </row>
     <row r="13">
@@ -1837,7 +1837,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2928575123673366</v>
+        <v>0.2928575123673372</v>
       </c>
     </row>
     <row r="14">
@@ -1845,7 +1845,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1324934874139426</v>
+        <v>0.1324934874139425</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1711,6 +1711,19 @@
         <v>-0.75</v>
       </c>
       <c r="C61" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C62" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1749,7 +1762,7 @@
         <v>-6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2976511656361516</v>
+        <v>0.292857512367337</v>
       </c>
     </row>
     <row r="3">
@@ -1757,7 +1770,7 @@
         <v>-5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3566248739311929</v>
+        <v>0.3517197002157845</v>
       </c>
     </row>
     <row r="4">
@@ -1765,7 +1778,7 @@
         <v>-4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5483961684511525</v>
+        <v>0.5424762654665015</v>
       </c>
     </row>
     <row r="5">
@@ -1773,7 +1786,7 @@
         <v>-3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.167040601292703</v>
+        <v>0.1632151961958194</v>
       </c>
     </row>
     <row r="6">
@@ -1781,7 +1794,7 @@
         <v>-2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5492825049004871</v>
+        <v>0.555592972789785</v>
       </c>
     </row>
     <row r="7">
@@ -1789,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5312969601400083</v>
+        <v>0.538170406519916</v>
       </c>
     </row>
     <row r="8">
@@ -1797,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3011178656411544</v>
+        <v>0.2959083342086755</v>
       </c>
     </row>
     <row r="9">
@@ -1805,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5448133237224131</v>
+        <v>0.5453234199068331</v>
       </c>
     </row>
     <row r="10">
@@ -1813,7 +1826,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4684837072372267</v>
+        <v>0.4690439829922903</v>
       </c>
     </row>
     <row r="11">
@@ -1821,7 +1834,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2183543475022113</v>
+        <v>0.2192088291740117</v>
       </c>
     </row>
     <row r="12">
@@ -1829,7 +1842,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3891470171057813</v>
+        <v>0.389761403016307</v>
       </c>
     </row>
     <row r="13">
@@ -1837,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2928575123673372</v>
+        <v>0.2935975262985582</v>
       </c>
     </row>
     <row r="14">
@@ -1845,7 +1858,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1324934874139425</v>
+        <v>0.1334391084576979</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
@@ -479,22 +479,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317482</v>
+        <v>0.7528155157766572</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0983684493577328</v>
+        <v>0.09740197126696939</v>
       </c>
       <c r="D2" t="n">
-        <v>7.719677351730598</v>
+        <v>7.72895564621852</v>
       </c>
       <c r="E2" t="n">
-        <v>1.166245428296781e-14</v>
+        <v>1.084324423553607e-14</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6461324144175186</v>
+        <v>0.6453774229440155</v>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -507,22 +507,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784787</v>
+        <v>0.4955801787492594</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2497200161268359</v>
+        <v>0.247585792167275</v>
       </c>
       <c r="D3" t="n">
-        <v>2.036880535920393</v>
+        <v>2.001650314467291</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04166201509511585</v>
+        <v>0.04532235360035365</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06813509891921965</v>
+        <v>0.06566784495054057</v>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.78532719206474</v>
+        <v>0.7832015268540737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08298603259787443</v>
+        <v>0.08329397343004262</v>
       </c>
       <c r="D4" t="n">
-        <v>9.463365912071028</v>
+        <v>9.402859469921593</v>
       </c>
       <c r="E4" t="n">
-        <v>2.981867513211542e-21</v>
+        <v>5.309998101258408e-21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5665963324726648</v>
+        <v>0.5641614537392891</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -563,22 +563,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384848</v>
+        <v>0.7414916060624751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08844092520571625</v>
+        <v>0.08939094365530947</v>
       </c>
       <c r="D5" t="n">
-        <v>8.421684761958419</v>
+        <v>8.294929841233792</v>
       </c>
       <c r="E5" t="n">
-        <v>3.711084974411862e-17</v>
+        <v>1.086493105121796e-16</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5322519496799432</v>
+        <v>0.528787836855631</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5226161616438579</v>
+        <v>0.5246183981741179</v>
       </c>
       <c r="C2" t="n">
-        <v>8.586137185972025e-05</v>
+        <v>7.819713468435813e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.458742931602504</v>
+        <v>2.456358233954639</v>
       </c>
     </row>
     <row r="3">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04686770450590967</v>
+        <v>-0.05673785255341926</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7373004278414821</v>
+        <v>0.6791000051656895</v>
       </c>
       <c r="D3" t="n">
-        <v>1.138253472208504</v>
+        <v>1.139421852536823</v>
       </c>
     </row>
     <row r="4">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3502322748046927</v>
+        <v>0.3487143655079766</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001386710077750293</v>
+        <v>0.001463088462194364</v>
       </c>
       <c r="D4" t="n">
-        <v>2.517208064570842</v>
+        <v>2.519813461187631</v>
       </c>
     </row>
     <row r="5"/>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009252282929502687</v>
+        <v>-0.009869518125738379</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6548326921534746</v>
+        <v>0.6296984436010151</v>
       </c>
     </row>
     <row r="7">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6739269320410703</v>
+        <v>0.6727517647121829</v>
       </c>
     </row>
     <row r="8">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6910886724599614</v>
+        <v>0.6896783975718975</v>
       </c>
     </row>
     <row r="9">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9751202219394079</v>
+        <v>0.9751202219394084</v>
       </c>
     </row>
   </sheetData>
@@ -753,7 +753,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7593726906317482</v>
+        <v>0.7528155157766572</v>
       </c>
       <c r="C2" t="n">
-        <v>1.166245428296781e-14</v>
+        <v>1.084324423553607e-14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6461324144175186</v>
+        <v>0.6453774229440155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1178420405386001</v>
+        <v>0.1178956983889718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1233470982376352</v>
+        <v>0.123472636476161</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01611484024392029</v>
+        <v>0.01605382162055646</v>
       </c>
     </row>
     <row r="3">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5086498402784787</v>
+        <v>0.4955801787492594</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04166201509511585</v>
+        <v>0.04532235360035365</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06813509891921965</v>
+        <v>0.06566784495054057</v>
       </c>
       <c r="E3" t="n">
-        <v>0.360980915943826</v>
+        <v>0.3684957581716648</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0665400416004828</v>
+        <v>0.05536696497405169</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03531899880137612</v>
+        <v>0.03743447742544159</v>
       </c>
     </row>
     <row r="4">
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.78532719206474</v>
+        <v>0.7832015268540737</v>
       </c>
       <c r="C4" t="n">
-        <v>2.981867513211542e-21</v>
+        <v>5.309998101258408e-21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5665963324726648</v>
+        <v>0.5641614537392891</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07271647745080442</v>
+        <v>0.07517513526349823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.480748434033649</v>
+        <v>0.4671144585715888</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00503528521451968</v>
+        <v>0.005359036019082497</v>
       </c>
     </row>
     <row r="5">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448215921384848</v>
+        <v>0.7414916060624751</v>
       </c>
       <c r="C5" t="n">
-        <v>3.711084974411862e-17</v>
+        <v>1.086493105121796e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5322519496799432</v>
+        <v>0.528787836855631</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06931932641661423</v>
+        <v>0.07191255053464399</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5117917730777792</v>
+        <v>0.4962013139949861</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004762160497665757</v>
+        <v>0.005128144382067545</v>
       </c>
     </row>
   </sheetData>
@@ -1762,7 +1762,7 @@
         <v>-6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.292857512367337</v>
+        <v>0.2928575123673366</v>
       </c>
     </row>
     <row r="3">
@@ -1770,7 +1770,7 @@
         <v>-5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3517197002157845</v>
+        <v>0.3517197002157838</v>
       </c>
     </row>
     <row r="4">
@@ -1778,7 +1778,7 @@
         <v>-4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5424762654665015</v>
+        <v>0.5424762654665025</v>
       </c>
     </row>
     <row r="5">
@@ -1786,7 +1786,7 @@
         <v>-3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1632151961958194</v>
+        <v>0.1632151961958191</v>
       </c>
     </row>
     <row r="6">
@@ -1794,7 +1794,7 @@
         <v>-2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.555592972789785</v>
+        <v>0.5555929727897858</v>
       </c>
     </row>
     <row r="7">
@@ -1802,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.538170406519916</v>
+        <v>0.5381704065199158</v>
       </c>
     </row>
     <row r="8">
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2959083342086755</v>
+        <v>0.2959083342086762</v>
       </c>
     </row>
     <row r="9">
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5453234199068331</v>
+        <v>0.545323419906833</v>
       </c>
     </row>
     <row r="10">
@@ -1826,7 +1826,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4690439829922903</v>
+        <v>0.4690439829922911</v>
       </c>
     </row>
     <row r="11">
@@ -1834,7 +1834,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2192088291740117</v>
+        <v>0.2192088291740119</v>
       </c>
     </row>
     <row r="12">
@@ -1850,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2935975262985582</v>
+        <v>0.2935975262985576</v>
       </c>
     </row>
     <row r="14">
@@ -1858,7 +1858,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1334391084576979</v>
+        <v>0.1334391084576978</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
@@ -482,13 +482,13 @@
         <v>0.7528155157766572</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09740197126696939</v>
+        <v>0.09740197126696934</v>
       </c>
       <c r="D2" t="n">
-        <v>7.72895564621852</v>
+        <v>7.728955646218525</v>
       </c>
       <c r="E2" t="n">
-        <v>1.084324423553607e-14</v>
+        <v>1.084324423553568e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6453774229440155</v>
@@ -510,13 +510,13 @@
         <v>0.4955801787492594</v>
       </c>
       <c r="C3" t="n">
-        <v>0.247585792167275</v>
+        <v>0.2475857921672751</v>
       </c>
       <c r="D3" t="n">
         <v>2.001650314467291</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04532235360035365</v>
+        <v>0.04532235360035364</v>
       </c>
       <c r="F3" t="n">
         <v>0.06566784495054057</v>
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7832015268540737</v>
+        <v>0.7832015268540738</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08329397343004262</v>
+        <v>0.08329397343004256</v>
       </c>
       <c r="D4" t="n">
-        <v>9.402859469921593</v>
+        <v>9.4028594699216</v>
       </c>
       <c r="E4" t="n">
-        <v>5.309998101258408e-21</v>
+        <v>5.309998101258028e-21</v>
       </c>
       <c r="F4" t="n">
         <v>0.5641614537392891</v>
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7414916060624751</v>
+        <v>0.741491606062475</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08939094365530947</v>
+        <v>0.08939094365530945</v>
       </c>
       <c r="D5" t="n">
-        <v>8.294929841233792</v>
+        <v>8.294929841233794</v>
       </c>
       <c r="E5" t="n">
-        <v>1.086493105121796e-16</v>
+        <v>1.086493105121773e-16</v>
       </c>
       <c r="F5" t="n">
-        <v>0.528787836855631</v>
+        <v>0.5287878368556311</v>
       </c>
       <c r="G5" t="n">
         <v>59</v>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5246183981741179</v>
+        <v>0.5246183981741185</v>
       </c>
       <c r="C2" t="n">
-        <v>7.819713468435813e-05</v>
+        <v>7.819713468435665e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.456358233954639</v>
+        <v>2.45635823395464</v>
       </c>
     </row>
     <row r="3">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.05673785255341926</v>
+        <v>-0.05673785255341895</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6791000051656895</v>
+        <v>0.6791000051656915</v>
       </c>
       <c r="D3" t="n">
         <v>1.139421852536823</v>
@@ -668,7 +668,7 @@
         <v>0.3487143655079766</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001463088462194364</v>
+        <v>0.001463088462194365</v>
       </c>
       <c r="D4" t="n">
         <v>2.519813461187631</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009869518125738379</v>
+        <v>-0.009869518125738417</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6296984436010151</v>
+        <v>0.6296984436010135</v>
       </c>
     </row>
     <row r="7">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9751202219394084</v>
+        <v>0.9751202219394079</v>
       </c>
     </row>
   </sheetData>
@@ -753,7 +753,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -808,7 +808,7 @@
         <v>0.7528155157766572</v>
       </c>
       <c r="C2" t="n">
-        <v>1.084324423553607e-14</v>
+        <v>1.084324423553568e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6453774229440155</v>
@@ -817,10 +817,10 @@
         <v>0.1178956983889718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.123472636476161</v>
+        <v>0.1234726364761612</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01605382162055646</v>
+        <v>0.01605382162055624</v>
       </c>
     </row>
     <row r="3">
@@ -833,16 +833,16 @@
         <v>0.4955801787492594</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04532235360035365</v>
+        <v>0.04532235360035364</v>
       </c>
       <c r="D3" t="n">
         <v>0.06566784495054057</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3684957581716648</v>
+        <v>0.3684957581716647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05536696497405169</v>
+        <v>0.05536696497405187</v>
       </c>
       <c r="G3" t="n">
         <v>0.03743447742544159</v>
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7832015268540737</v>
+        <v>0.7832015268540738</v>
       </c>
       <c r="C4" t="n">
-        <v>5.309998101258408e-21</v>
+        <v>5.309998101258028e-21</v>
       </c>
       <c r="D4" t="n">
         <v>0.5641614537392891</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07517513526349823</v>
+        <v>0.07517513526349826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4671144585715888</v>
+        <v>0.4671144585715886</v>
       </c>
       <c r="G4" t="n">
         <v>0.005359036019082497</v>
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7414916060624751</v>
+        <v>0.741491606062475</v>
       </c>
       <c r="C5" t="n">
-        <v>1.086493105121796e-16</v>
+        <v>1.086493105121773e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.528787836855631</v>
+        <v>0.5287878368556311</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07191255053464399</v>
+        <v>0.07191255053464393</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4962013139949861</v>
+        <v>0.496201313994986</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005128144382067545</v>
+        <v>0.005128144382067101</v>
       </c>
     </row>
   </sheetData>
@@ -1762,7 +1762,7 @@
         <v>-6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2928575123673366</v>
+        <v>0.292857512367337</v>
       </c>
     </row>
     <row r="3">
@@ -1770,7 +1770,7 @@
         <v>-5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3517197002157838</v>
+        <v>0.3517197002157845</v>
       </c>
     </row>
     <row r="4">
@@ -1778,7 +1778,7 @@
         <v>-4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5424762654665025</v>
+        <v>0.5424762654665015</v>
       </c>
     </row>
     <row r="5">
@@ -1786,7 +1786,7 @@
         <v>-3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1632151961958191</v>
+        <v>0.1632151961958194</v>
       </c>
     </row>
     <row r="6">
@@ -1794,7 +1794,7 @@
         <v>-2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5555929727897858</v>
+        <v>0.555592972789785</v>
       </c>
     </row>
     <row r="7">
@@ -1802,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5381704065199158</v>
+        <v>0.538170406519916</v>
       </c>
     </row>
     <row r="8">
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2959083342086762</v>
+        <v>0.2959083342086755</v>
       </c>
     </row>
     <row r="9">
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.545323419906833</v>
+        <v>0.5453234199068331</v>
       </c>
     </row>
     <row r="10">
@@ -1826,7 +1826,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4690439829922911</v>
+        <v>0.4690439829922903</v>
       </c>
     </row>
     <row r="11">
@@ -1834,7 +1834,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2192088291740119</v>
+        <v>0.2192088291740117</v>
       </c>
     </row>
     <row r="12">
@@ -1850,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2935975262985576</v>
+        <v>0.2935975262985582</v>
       </c>
     </row>
     <row r="14">
@@ -1858,7 +1858,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1334391084576978</v>
+        <v>0.1334391084576979</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -479,16 +479,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766572</v>
+        <v>0.7528155157766573</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09740197126696934</v>
+        <v>0.09740197126696931</v>
       </c>
       <c r="D2" t="n">
-        <v>7.728955646218525</v>
+        <v>7.728955646218528</v>
       </c>
       <c r="E2" t="n">
-        <v>1.084324423553568e-14</v>
+        <v>1.084324423553544e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6453774229440155</v>
@@ -519,7 +519,7 @@
         <v>0.04532235360035364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06566784495054057</v>
+        <v>0.06566784495054068</v>
       </c>
       <c r="G3" t="n">
         <v>59</v>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5246183981741185</v>
+        <v>0.5246183981741184</v>
       </c>
       <c r="C2" t="n">
-        <v>7.819713468435665e-05</v>
+        <v>7.819713468435733e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.45635823395464</v>
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.05673785255341895</v>
+        <v>-0.05673785255341901</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6791000051656915</v>
+        <v>0.6791000051656908</v>
       </c>
       <c r="D3" t="n">
-        <v>1.139421852536823</v>
+        <v>1.139421852536822</v>
       </c>
     </row>
     <row r="4">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3487143655079766</v>
+        <v>0.3487143655079768</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001463088462194365</v>
+        <v>0.001463088462194355</v>
       </c>
       <c r="D4" t="n">
         <v>2.519813461187631</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009869518125738417</v>
+        <v>-0.009869518125738452</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6296984436010135</v>
+        <v>0.6296984436010122</v>
       </c>
     </row>
     <row r="7">
@@ -757,7 +757,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766572</v>
+        <v>0.7528155157766573</v>
       </c>
       <c r="C2" t="n">
-        <v>1.084324423553568e-14</v>
+        <v>1.084324423553544e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6453774229440155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1178956983889718</v>
+        <v>0.1178956983889717</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1234726364761612</v>
+        <v>0.1234726364761613</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01605382162055624</v>
+        <v>0.01605382162055646</v>
       </c>
     </row>
     <row r="3">
@@ -836,13 +836,13 @@
         <v>0.04532235360035364</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06566784495054057</v>
+        <v>0.06566784495054068</v>
       </c>
       <c r="E3" t="n">
         <v>0.3684957581716647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05536696497405187</v>
+        <v>0.05536696497405195</v>
       </c>
       <c r="G3" t="n">
         <v>0.03743447742544159</v>
@@ -867,7 +867,7 @@
         <v>0.07517513526349826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4671144585715886</v>
+        <v>0.4671144585715887</v>
       </c>
       <c r="G4" t="n">
         <v>0.005359036019082497</v>
@@ -892,7 +892,7 @@
         <v>0.07191255053464393</v>
       </c>
       <c r="F5" t="n">
-        <v>0.496201313994986</v>
+        <v>0.4962013139949859</v>
       </c>
       <c r="G5" t="n">
         <v>0.005128144382067101</v>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -479,16 +479,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766573</v>
+        <v>0.7528155157766572</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09740197126696931</v>
+        <v>0.09740197126696934</v>
       </c>
       <c r="D2" t="n">
-        <v>7.728955646218528</v>
+        <v>7.728955646218525</v>
       </c>
       <c r="E2" t="n">
-        <v>1.084324423553544e-14</v>
+        <v>1.084324423553568e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6453774229440155</v>
@@ -519,7 +519,7 @@
         <v>0.04532235360035364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06566784495054068</v>
+        <v>0.06566784495054057</v>
       </c>
       <c r="G3" t="n">
         <v>59</v>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5246183981741184</v>
+        <v>0.5246183981741185</v>
       </c>
       <c r="C2" t="n">
-        <v>7.819713468435733e-05</v>
+        <v>7.819713468435665e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.45635823395464</v>
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.05673785255341901</v>
+        <v>-0.05673785255341895</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6791000051656908</v>
+        <v>0.6791000051656915</v>
       </c>
       <c r="D3" t="n">
-        <v>1.139421852536822</v>
+        <v>1.139421852536823</v>
       </c>
     </row>
     <row r="4">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3487143655079768</v>
+        <v>0.3487143655079766</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001463088462194355</v>
+        <v>0.001463088462194365</v>
       </c>
       <c r="D4" t="n">
         <v>2.519813461187631</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009869518125738452</v>
+        <v>-0.009869518125738417</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6296984436010122</v>
+        <v>0.6296984436010135</v>
       </c>
     </row>
     <row r="7">
@@ -757,7 +757,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766573</v>
+        <v>0.7528155157766572</v>
       </c>
       <c r="C2" t="n">
-        <v>1.084324423553544e-14</v>
+        <v>1.084324423553568e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6453774229440155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1178956983889717</v>
+        <v>0.1178956983889718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1234726364761613</v>
+        <v>0.1234726364761612</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01605382162055646</v>
+        <v>0.01605382162055624</v>
       </c>
     </row>
     <row r="3">
@@ -836,13 +836,13 @@
         <v>0.04532235360035364</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06566784495054068</v>
+        <v>0.06566784495054057</v>
       </c>
       <c r="E3" t="n">
         <v>0.3684957581716647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05536696497405195</v>
+        <v>0.05536696497405187</v>
       </c>
       <c r="G3" t="n">
         <v>0.03743447742544159</v>
@@ -867,7 +867,7 @@
         <v>0.07517513526349826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4671144585715887</v>
+        <v>0.4671144585715886</v>
       </c>
       <c r="G4" t="n">
         <v>0.005359036019082497</v>
@@ -892,7 +892,7 @@
         <v>0.07191255053464393</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4962013139949859</v>
+        <v>0.496201313994986</v>
       </c>
       <c r="G5" t="n">
         <v>0.005128144382067101</v>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7832015268540738</v>
+        <v>0.7786262253612442</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08329397343004256</v>
+        <v>0.08278274868449487</v>
       </c>
       <c r="D4" t="n">
-        <v>9.4028594699216</v>
+        <v>9.405658035453468</v>
       </c>
       <c r="E4" t="n">
-        <v>5.309998101258028e-21</v>
+        <v>5.17056432496023e-21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5641614537392891</v>
+        <v>0.565742225548316</v>
       </c>
       <c r="G4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -563,22 +563,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.741491606062475</v>
+        <v>0.7193521031207601</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08939094365530945</v>
+        <v>0.09312880850449586</v>
       </c>
       <c r="D5" t="n">
-        <v>8.294929841233794</v>
+        <v>7.724270445122606</v>
       </c>
       <c r="E5" t="n">
-        <v>1.086493105121773e-16</v>
+        <v>1.124957722325633e-14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5287878368556311</v>
+        <v>0.5227665260457355</v>
       </c>
       <c r="G5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9751202219394079</v>
+        <v>0.971896526695238</v>
       </c>
     </row>
   </sheetData>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7832015268540738</v>
+        <v>0.7786262253612442</v>
       </c>
       <c r="C4" t="n">
-        <v>5.309998101258028e-21</v>
+        <v>5.17056432496023e-21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5641614537392891</v>
+        <v>0.565742225548316</v>
       </c>
       <c r="E4" t="n">
         <v>0.07517513526349826</v>
@@ -880,13 +880,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.741491606062475</v>
+        <v>0.7193521031207601</v>
       </c>
       <c r="C5" t="n">
-        <v>1.086493105121773e-16</v>
+        <v>1.124957722325633e-14</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5287878368556311</v>
+        <v>0.5227665260457355</v>
       </c>
       <c r="E5" t="n">
         <v>0.07191255053464393</v>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -424,7 +424,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -479,16 +479,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766572</v>
+        <v>0.7528155157766573</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09740197126696934</v>
+        <v>0.09740197126696931</v>
       </c>
       <c r="D2" t="n">
-        <v>7.728955646218525</v>
+        <v>7.728955646218528</v>
       </c>
       <c r="E2" t="n">
-        <v>1.084324423553568e-14</v>
+        <v>1.084324423553544e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6453774229440155</v>
@@ -519,7 +519,7 @@
         <v>0.04532235360035364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06566784495054057</v>
+        <v>0.06566784495054068</v>
       </c>
       <c r="G3" t="n">
         <v>59</v>
@@ -575,7 +575,7 @@
         <v>1.124957722325633e-14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5227665260457355</v>
+        <v>0.5227665260457356</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5246183981741185</v>
+        <v>0.5246183981741184</v>
       </c>
       <c r="C2" t="n">
-        <v>7.819713468435665e-05</v>
+        <v>7.819713468435733e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.45635823395464</v>
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.05673785255341895</v>
+        <v>-0.05673785255341901</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6791000051656915</v>
+        <v>0.6791000051656908</v>
       </c>
       <c r="D3" t="n">
-        <v>1.139421852536823</v>
+        <v>1.139421852536822</v>
       </c>
     </row>
     <row r="4">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3487143655079766</v>
+        <v>0.3487143655079768</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001463088462194365</v>
+        <v>0.001463088462194355</v>
       </c>
       <c r="D4" t="n">
         <v>2.519813461187631</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009869518125738417</v>
+        <v>-0.009869518125738452</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6296984436010135</v>
+        <v>0.6296984436010122</v>
       </c>
     </row>
     <row r="7">
@@ -754,10 +754,10 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766572</v>
+        <v>0.7528155157766573</v>
       </c>
       <c r="C2" t="n">
-        <v>1.084324423553568e-14</v>
+        <v>1.084324423553544e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6453774229440155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1178956983889718</v>
+        <v>0.1178956983889717</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1234726364761612</v>
+        <v>0.1234726364761613</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01605382162055624</v>
+        <v>0.01605382162055646</v>
       </c>
     </row>
     <row r="3">
@@ -836,13 +836,13 @@
         <v>0.04532235360035364</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06566784495054057</v>
+        <v>0.06566784495054068</v>
       </c>
       <c r="E3" t="n">
         <v>0.3684957581716647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05536696497405187</v>
+        <v>0.05536696497405195</v>
       </c>
       <c r="G3" t="n">
         <v>0.03743447742544159</v>
@@ -867,7 +867,7 @@
         <v>0.07517513526349826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4671144585715886</v>
+        <v>0.4671144585715887</v>
       </c>
       <c r="G4" t="n">
         <v>0.005359036019082497</v>
@@ -886,13 +886,13 @@
         <v>1.124957722325633e-14</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5227665260457355</v>
+        <v>0.5227665260457356</v>
       </c>
       <c r="E5" t="n">
         <v>0.07191255053464393</v>
       </c>
       <c r="F5" t="n">
-        <v>0.496201313994986</v>
+        <v>0.4962013139949859</v>
       </c>
       <c r="G5" t="n">
         <v>0.005128144382067101</v>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -507,22 +507,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4955801787492594</v>
+        <v>0.5037673569696937</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2475857921672751</v>
+        <v>0.2462403604206437</v>
       </c>
       <c r="D3" t="n">
-        <v>2.001650314467291</v>
+        <v>2.045835849611029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04532235360035364</v>
+        <v>0.04077252360637791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06566784495054068</v>
+        <v>0.06783181437820096</v>
       </c>
       <c r="G3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5246183981741184</v>
+        <v>0.5200186943042363</v>
       </c>
       <c r="C2" t="n">
-        <v>7.819713468435733e-05</v>
+        <v>7.795634348994887e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.45635823395464</v>
+        <v>2.502674222133993</v>
       </c>
     </row>
     <row r="3">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.05673785255341901</v>
+        <v>-0.05907301617179483</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6791000051656908</v>
+        <v>0.6690100436183404</v>
       </c>
       <c r="D3" t="n">
-        <v>1.139421852536822</v>
+        <v>1.145136180437108</v>
       </c>
     </row>
     <row r="4">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3487143655079768</v>
+        <v>0.3453715604597031</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001463088462194355</v>
+        <v>0.001767810950831978</v>
       </c>
       <c r="D4" t="n">
-        <v>2.519813461187631</v>
+        <v>2.567713027907435</v>
       </c>
     </row>
     <row r="5"/>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.009869518125738452</v>
+        <v>-0.01066512994448654</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6296984436010122</v>
+        <v>0.6009074659089468</v>
       </c>
     </row>
     <row r="7">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6727517647121829</v>
+        <v>0.6721219230157129</v>
       </c>
     </row>
     <row r="8">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6896783975718975</v>
+        <v>0.6887936896420327</v>
       </c>
     </row>
     <row r="9">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4955801787492594</v>
+        <v>0.5037673569696937</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04532235360035364</v>
+        <v>0.04077252360637791</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06566784495054068</v>
+        <v>0.06783181437820096</v>
       </c>
       <c r="E3" t="n">
         <v>0.3684957581716647</v>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -423,8 +423,8 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -479,16 +479,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766573</v>
+        <v>0.7528155157766572</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09740197126696931</v>
+        <v>0.09740197126696934</v>
       </c>
       <c r="D2" t="n">
-        <v>7.728955646218528</v>
+        <v>7.728955646218525</v>
       </c>
       <c r="E2" t="n">
-        <v>1.084324423553544e-14</v>
+        <v>1.084324423553568e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6453774229440155</v>
@@ -510,13 +510,13 @@
         <v>0.5037673569696937</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2462403604206437</v>
+        <v>0.2462403604206438</v>
       </c>
       <c r="D3" t="n">
         <v>2.045835849611029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04077252360637791</v>
+        <v>0.04077252360637795</v>
       </c>
       <c r="F3" t="n">
         <v>0.06783181437820096</v>
@@ -575,7 +575,7 @@
         <v>1.124957722325633e-14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5227665260457356</v>
+        <v>0.5227665260457355</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -636,7 +636,7 @@
         <v>0.5200186943042363</v>
       </c>
       <c r="C2" t="n">
-        <v>7.795634348994887e-05</v>
+        <v>7.795634348994842e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.502674222133993</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.05907301617179483</v>
+        <v>-0.05907301617179508</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6690100436183404</v>
+        <v>0.6690100436183393</v>
       </c>
       <c r="D3" t="n">
         <v>1.145136180437108</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3453715604597031</v>
+        <v>0.3453715604597029</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001767810950831978</v>
+        <v>0.001767810950831996</v>
       </c>
       <c r="D4" t="n">
         <v>2.567713027907435</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.01066512994448654</v>
+        <v>-0.01066512994448651</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6009074659089468</v>
+        <v>0.6009074659089484</v>
       </c>
     </row>
     <row r="7">
@@ -754,10 +754,10 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766573</v>
+        <v>0.7528155157766572</v>
       </c>
       <c r="C2" t="n">
-        <v>1.084324423553544e-14</v>
+        <v>1.084324423553568e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6453774229440155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1178956983889717</v>
+        <v>0.1178956983889718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1234726364761613</v>
+        <v>0.1234726364761612</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01605382162055646</v>
+        <v>0.01605382162055624</v>
       </c>
     </row>
     <row r="3">
@@ -833,7 +833,7 @@
         <v>0.5037673569696937</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04077252360637791</v>
+        <v>0.04077252360637795</v>
       </c>
       <c r="D3" t="n">
         <v>0.06783181437820096</v>
@@ -842,7 +842,7 @@
         <v>0.3684957581716647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05536696497405195</v>
+        <v>0.05536696497405187</v>
       </c>
       <c r="G3" t="n">
         <v>0.03743447742544159</v>
@@ -867,7 +867,7 @@
         <v>0.07517513526349826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4671144585715887</v>
+        <v>0.4671144585715886</v>
       </c>
       <c r="G4" t="n">
         <v>0.005359036019082497</v>
@@ -886,13 +886,13 @@
         <v>1.124957722325633e-14</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5227665260457356</v>
+        <v>0.5227665260457355</v>
       </c>
       <c r="E5" t="n">
         <v>0.07191255053464393</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4962013139949859</v>
+        <v>0.496201313994986</v>
       </c>
       <c r="G5" t="n">
         <v>0.005128144382067101</v>

--- a/site/data/downloads/regression_analysis.xlsx
+++ b/site/data/downloads/regression_analysis.xlsx
@@ -423,8 +423,8 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -479,16 +479,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766572</v>
+        <v>0.7528155157766573</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09740197126696934</v>
+        <v>0.09740197126696931</v>
       </c>
       <c r="D2" t="n">
-        <v>7.728955646218525</v>
+        <v>7.728955646218528</v>
       </c>
       <c r="E2" t="n">
-        <v>1.084324423553568e-14</v>
+        <v>1.084324423553544e-14</v>
       </c>
       <c r="F2" t="n">
         <v>0.6453774229440155</v>
@@ -510,13 +510,13 @@
         <v>0.5037673569696937</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2462403604206438</v>
+        <v>0.2462403604206437</v>
       </c>
       <c r="D3" t="n">
         <v>2.045835849611029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04077252360637795</v>
+        <v>0.04077252360637791</v>
       </c>
       <c r="F3" t="n">
         <v>0.06783181437820096</v>
@@ -575,7 +575,7 @@
         <v>1.124957722325633e-14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5227665260457355</v>
+        <v>0.5227665260457356</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -636,7 +636,7 @@
         <v>0.5200186943042363</v>
       </c>
       <c r="C2" t="n">
-        <v>7.795634348994842e-05</v>
+        <v>7.795634348994887e-05</v>
       </c>
       <c r="D2" t="n">
         <v>2.502674222133993</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.05907301617179508</v>
+        <v>-0.05907301617179483</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6690100436183393</v>
+        <v>0.6690100436183404</v>
       </c>
       <c r="D3" t="n">
         <v>1.145136180437108</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3453715604597029</v>
+        <v>0.3453715604597031</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001767810950831996</v>
+        <v>0.001767810950831978</v>
       </c>
       <c r="D4" t="n">
         <v>2.567713027907435</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.01066512994448651</v>
+        <v>-0.01066512994448654</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6009074659089484</v>
+        <v>0.6009074659089468</v>
       </c>
     </row>
     <row r="7">
@@ -754,10 +754,10 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7528155157766572</v>
+        <v>0.7528155157766573</v>
       </c>
       <c r="C2" t="n">
-        <v>1.084324423553568e-14</v>
+        <v>1.084324423553544e-14</v>
       </c>
       <c r="D2" t="n">
         <v>0.6453774229440155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1178956983889718</v>
+        <v>0.1178956983889717</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1234726364761612</v>
+        <v>0.1234726364761613</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01605382162055624</v>
+        <v>0.01605382162055646</v>
       </c>
     </row>
     <row r="3">
@@ -833,7 +833,7 @@
         <v>0.5037673569696937</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04077252360637795</v>
+        <v>0.04077252360637791</v>
       </c>
       <c r="D3" t="n">
         <v>0.06783181437820096</v>
@@ -842,7 +842,7 @@
         <v>0.3684957581716647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05536696497405187</v>
+        <v>0.05536696497405195</v>
       </c>
       <c r="G3" t="n">
         <v>0.03743447742544159</v>
@@ -867,7 +867,7 @@
         <v>0.07517513526349826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4671144585715886</v>
+        <v>0.4671144585715887</v>
       </c>
       <c r="G4" t="n">
         <v>0.005359036019082497</v>
@@ -886,13 +886,13 @@
         <v>1.124957722325633e-14</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5227665260457355</v>
+        <v>0.5227665260457356</v>
       </c>
       <c r="E5" t="n">
         <v>0.07191255053464393</v>
       </c>
       <c r="F5" t="n">
-        <v>0.496201313994986</v>
+        <v>0.4962013139949859</v>
       </c>
       <c r="G5" t="n">
         <v>0.005128144382067101</v>
